--- a/artfynd/A 35926-2024 artfynd.xlsx
+++ b/artfynd/A 35926-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>95161211</v>
       </c>
       <c r="B2" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406342.2535867052</v>
+        <v>406343</v>
       </c>
       <c r="R2" t="n">
-        <v>6618545.451032135</v>
+        <v>6618546</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,19 +752,9 @@
           <t>2021-06-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
